--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/3_fold/161.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/3_fold/161.xlsx
@@ -426,13 +426,13 @@
         <v>-13.86394014182072</v>
       </c>
       <c r="E2">
-        <v>-11.27144633738324</v>
+        <v>-8.309249220167857</v>
       </c>
       <c r="F2">
-        <v>-1.802718043367856</v>
+        <v>-1.364804353277863</v>
       </c>
       <c r="G2">
-        <v>-10.98985033956439</v>
+        <v>-10.13900371997076</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-13.02836255484475</v>
       </c>
       <c r="E3">
-        <v>-11.76420770805389</v>
+        <v>-8.527259015845123</v>
       </c>
       <c r="F3">
-        <v>-1.619681232190942</v>
+        <v>-1.509371364062838</v>
       </c>
       <c r="G3">
-        <v>-10.49860510808302</v>
+        <v>-9.87706011472147</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-12.0984366038441</v>
       </c>
       <c r="E4">
-        <v>-12.73110483580162</v>
+        <v>-9.705577009588966</v>
       </c>
       <c r="F4">
-        <v>-1.688607281042697</v>
+        <v>-1.191918305165958</v>
       </c>
       <c r="G4">
-        <v>-10.05664727859032</v>
+        <v>-9.016953899254501</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-11.16512460721472</v>
       </c>
       <c r="E5">
-        <v>-13.02026601508741</v>
+        <v>-10.11163168843474</v>
       </c>
       <c r="F5">
-        <v>-1.529896192726933</v>
+        <v>-1.155501779493386</v>
       </c>
       <c r="G5">
-        <v>-10.02765352075738</v>
+        <v>-9.546624632810195</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-10.23917260704817</v>
       </c>
       <c r="E6">
-        <v>-13.30105857440701</v>
+        <v>-11.18926811956605</v>
       </c>
       <c r="F6">
-        <v>-1.218688478107589</v>
+        <v>-0.8719162715981789</v>
       </c>
       <c r="G6">
-        <v>-9.92076262638539</v>
+        <v>-8.700035374780072</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-9.337026594023229</v>
       </c>
       <c r="E7">
-        <v>-13.83642835701583</v>
+        <v>-11.05505773540072</v>
       </c>
       <c r="F7">
-        <v>-1.145578278227242</v>
+        <v>-0.705304866323245</v>
       </c>
       <c r="G7">
-        <v>-9.458451562917247</v>
+        <v>-8.922798673572089</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-8.483182082785149</v>
       </c>
       <c r="E8">
-        <v>-13.87667290552199</v>
+        <v>-12.47991491107016</v>
       </c>
       <c r="F8">
-        <v>-0.7559985008235039</v>
+        <v>-0.4511010624242284</v>
       </c>
       <c r="G8">
-        <v>-10.19406140283438</v>
+        <v>-8.914628247181168</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-7.682785818044972</v>
       </c>
       <c r="E9">
-        <v>-15.2345041374039</v>
+        <v>-12.94588130103741</v>
       </c>
       <c r="F9">
-        <v>-0.5696644139306449</v>
+        <v>-0.1804599748288658</v>
       </c>
       <c r="G9">
-        <v>-9.684313532334023</v>
+        <v>-8.08177775313902</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-6.957438899538412</v>
       </c>
       <c r="E10">
-        <v>-15.80125624488586</v>
+        <v>-12.84245095470222</v>
       </c>
       <c r="F10">
-        <v>-0.4117198392779534</v>
+        <v>-0.187452036445531</v>
       </c>
       <c r="G10">
-        <v>-8.631225685746319</v>
+        <v>-6.101230642087875</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-6.300581700479335</v>
       </c>
       <c r="E11">
-        <v>-16.85994101229507</v>
+        <v>-14.46834067699416</v>
       </c>
       <c r="F11">
-        <v>-0.2707327957148298</v>
+        <v>0.08079132039385632</v>
       </c>
       <c r="G11">
-        <v>-9.249364127747956</v>
+        <v>-6.895675497328939</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-5.728153909882332</v>
       </c>
       <c r="E12">
-        <v>-15.99729388467791</v>
+        <v>-16.00463906951835</v>
       </c>
       <c r="F12">
-        <v>-0.04410289550952939</v>
+        <v>-0.1319178048147313</v>
       </c>
       <c r="G12">
-        <v>-8.478698921115479</v>
+        <v>-8.202913924966492</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-5.227736904247307</v>
       </c>
       <c r="E13">
-        <v>-16.97400874407428</v>
+        <v>-15.63752473866453</v>
       </c>
       <c r="F13">
-        <v>0.3155757223577544</v>
+        <v>0.5984572729735484</v>
       </c>
       <c r="G13">
-        <v>-8.653098460124284</v>
+        <v>-6.590132007327444</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>-4.814112269788901</v>
       </c>
       <c r="E14">
-        <v>-18.25136899283988</v>
+        <v>-17.15070074290556</v>
       </c>
       <c r="F14">
-        <v>0.3707084845389902</v>
+        <v>0.7582848739596976</v>
       </c>
       <c r="G14">
-        <v>-7.875060668575848</v>
+        <v>-6.837975999124981</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>-4.474745639664118</v>
       </c>
       <c r="E15">
-        <v>-19.69392797340529</v>
+        <v>-17.40897320098503</v>
       </c>
       <c r="F15">
-        <v>0.5191302355221443</v>
+        <v>0.6462012552063016</v>
       </c>
       <c r="G15">
-        <v>-7.302515059741054</v>
+        <v>-6.109487142662817</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>-4.221668954930174</v>
       </c>
       <c r="E16">
-        <v>-19.97771385404397</v>
+        <v>-18.84244806269106</v>
       </c>
       <c r="F16">
-        <v>0.8335679183560271</v>
+        <v>1.091672389924771</v>
       </c>
       <c r="G16">
-        <v>-7.827603998270396</v>
+        <v>-5.086601403029884</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>-4.041250181631111</v>
       </c>
       <c r="E17">
-        <v>-19.84971653621717</v>
+        <v>-20.21222540900519</v>
       </c>
       <c r="F17">
-        <v>1.415806312225932</v>
+        <v>1.471988279576146</v>
       </c>
       <c r="G17">
-        <v>-7.712539366961948</v>
+        <v>-6.475252766569194</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>-3.939236826101762</v>
       </c>
       <c r="E18">
-        <v>-21.68280658673007</v>
+        <v>-19.8922389071492</v>
       </c>
       <c r="F18">
-        <v>1.485709507627514</v>
+        <v>1.54045663741834</v>
       </c>
       <c r="G18">
-        <v>-7.838737362918965</v>
+        <v>-4.972106185554191</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>-3.899593351491558</v>
       </c>
       <c r="E19">
-        <v>-21.99158058694307</v>
+        <v>-19.95206457726453</v>
       </c>
       <c r="F19">
-        <v>1.896335944794485</v>
+        <v>2.394292677256533</v>
       </c>
       <c r="G19">
-        <v>-8.265983128035147</v>
+        <v>-5.473256569289063</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>-3.922804528441338</v>
       </c>
       <c r="E20">
-        <v>-22.4584119154458</v>
+        <v>-21.90739172666648</v>
       </c>
       <c r="F20">
-        <v>2.268747558221901</v>
+        <v>2.703205602004405</v>
       </c>
       <c r="G20">
-        <v>-6.87900027944763</v>
+        <v>-5.26454984685679</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>-3.990798665796508</v>
       </c>
       <c r="E21">
-        <v>-23.2129870108699</v>
+        <v>-22.87471453097093</v>
       </c>
       <c r="F21">
-        <v>2.333820450581393</v>
+        <v>2.547524143104877</v>
       </c>
       <c r="G21">
-        <v>-7.068105261741879</v>
+        <v>-4.556490366917468</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>-4.099734812471111</v>
       </c>
       <c r="E22">
-        <v>-23.89586730580457</v>
+        <v>-22.34812545946299</v>
       </c>
       <c r="F22">
-        <v>2.366878727860276</v>
+        <v>2.944174375568094</v>
       </c>
       <c r="G22">
-        <v>-7.067572263910056</v>
+        <v>-3.647669473840124</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>-4.230693876614472</v>
       </c>
       <c r="E23">
-        <v>-25.10814885460594</v>
+        <v>-23.4943094016484</v>
       </c>
       <c r="F23">
-        <v>2.685895696348652</v>
+        <v>2.841151138356927</v>
       </c>
       <c r="G23">
-        <v>-6.934336048136548</v>
+        <v>-3.848338191703047</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>-4.378054242775452</v>
       </c>
       <c r="E24">
-        <v>-24.23322503395399</v>
+        <v>-23.93540541236554</v>
       </c>
       <c r="F24">
-        <v>3.172988206230785</v>
+        <v>3.069036917353171</v>
       </c>
       <c r="G24">
-        <v>-6.010611079041404</v>
+        <v>-4.320269700508311</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>-4.526090095017832</v>
       </c>
       <c r="E25">
-        <v>-25.05733484776587</v>
+        <v>-23.48107267212399</v>
       </c>
       <c r="F25">
-        <v>3.150857499768435</v>
+        <v>3.400981677229279</v>
       </c>
       <c r="G25">
-        <v>-6.603079550931533</v>
+        <v>-4.433351315038736</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>-4.672776172547448</v>
       </c>
       <c r="E26">
-        <v>-24.88154401526211</v>
+        <v>-25.19975082683309</v>
       </c>
       <c r="F26">
-        <v>3.055201662475892</v>
+        <v>3.125507119179995</v>
       </c>
       <c r="G26">
-        <v>-6.063026946564685</v>
+        <v>-4.606320698374578</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>-4.808045675739204</v>
       </c>
       <c r="E27">
-        <v>-25.24724999069955</v>
+        <v>-24.11316613106263</v>
       </c>
       <c r="F27">
-        <v>3.021221668354223</v>
+        <v>3.104282292501276</v>
       </c>
       <c r="G27">
-        <v>-6.014865130059368</v>
+        <v>-4.325255382090454</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>-4.932387108940754</v>
       </c>
       <c r="E28">
-        <v>-26.02415951992948</v>
+        <v>-24.0965602168765</v>
       </c>
       <c r="F28">
-        <v>2.868891331171765</v>
+        <v>3.052061173645575</v>
       </c>
       <c r="G28">
-        <v>-5.033758475132037</v>
+        <v>-4.358562780761061</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>-5.036376160004637</v>
       </c>
       <c r="E29">
-        <v>-24.99337015240753</v>
+        <v>-24.54035972657621</v>
       </c>
       <c r="F29">
-        <v>2.712793357616476</v>
+        <v>3.08750134462128</v>
       </c>
       <c r="G29">
-        <v>-5.987705414455188</v>
+        <v>-4.742023270574843</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>-5.119086175679592</v>
       </c>
       <c r="E30">
-        <v>-25.22393287803405</v>
+        <v>-24.40226844018631</v>
       </c>
       <c r="F30">
-        <v>2.832404330585955</v>
+        <v>2.813680175547714</v>
       </c>
       <c r="G30">
-        <v>-5.566484842220478</v>
+        <v>-3.761578724755367</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>-5.173442146811477</v>
       </c>
       <c r="E31">
-        <v>-25.44187927507521</v>
+        <v>-24.27281748220305</v>
       </c>
       <c r="F31">
-        <v>2.935649286625284</v>
+        <v>2.972657326457273</v>
       </c>
       <c r="G31">
-        <v>-5.992856623314293</v>
+        <v>-4.115555495996399</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>-5.203748378648736</v>
       </c>
       <c r="E32">
-        <v>-25.37283816035427</v>
+        <v>-23.26113827499346</v>
       </c>
       <c r="F32">
-        <v>2.676990517986136</v>
+        <v>2.874823893531001</v>
       </c>
       <c r="G32">
-        <v>-6.17842925351814</v>
+        <v>-4.312986500321915</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>-5.210325387263371</v>
       </c>
       <c r="E33">
-        <v>-24.32885281957396</v>
+        <v>-23.42940278369647</v>
       </c>
       <c r="F33">
-        <v>2.867247444431539</v>
+        <v>3.023074604275287</v>
       </c>
       <c r="G33">
-        <v>-6.414573777379893</v>
+        <v>-4.017907644770056</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>-5.204818214770958</v>
       </c>
       <c r="E34">
-        <v>-23.77788244400872</v>
+        <v>-23.62889564915637</v>
       </c>
       <c r="F34">
-        <v>2.345677656770288</v>
+        <v>2.747318146573055</v>
       </c>
       <c r="G34">
-        <v>-5.624704096074102</v>
+        <v>-3.860835501113796</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>-5.193313256809502</v>
       </c>
       <c r="E35">
-        <v>-22.99927020855191</v>
+        <v>-22.28796468227109</v>
       </c>
       <c r="F35">
-        <v>2.174686512786206</v>
+        <v>2.444424888009769</v>
       </c>
       <c r="G35">
-        <v>-5.984729234015383</v>
+        <v>-4.645454657194303</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>-5.190922207138318</v>
       </c>
       <c r="E36">
-        <v>-24.14371521671837</v>
+        <v>-23.07661654460291</v>
       </c>
       <c r="F36">
-        <v>2.176127685169256</v>
+        <v>2.522173762516437</v>
       </c>
       <c r="G36">
-        <v>-6.313261152241576</v>
+        <v>-3.97410250619442</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>-5.205546753598897</v>
       </c>
       <c r="E37">
-        <v>-22.48910591226979</v>
+        <v>-21.03878512725522</v>
       </c>
       <c r="F37">
-        <v>2.363926700033897</v>
+        <v>2.111959088887481</v>
       </c>
       <c r="G37">
-        <v>-5.996938525964215</v>
+        <v>-3.642352737704054</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>-5.251214939783436</v>
       </c>
       <c r="E38">
-        <v>-23.2642900929028</v>
+        <v>-21.01534121731751</v>
       </c>
       <c r="F38">
-        <v>2.103456171827486</v>
+        <v>2.092414574185042</v>
       </c>
       <c r="G38">
-        <v>-5.70688507854097</v>
+        <v>-4.432950739028485</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>-5.333112214526971</v>
       </c>
       <c r="E39">
-        <v>-22.22224293899777</v>
+        <v>-21.29353443255672</v>
       </c>
       <c r="F39">
-        <v>2.356012921574446</v>
+        <v>2.737600527075919</v>
       </c>
       <c r="G39">
-        <v>-5.752405079705949</v>
+        <v>-3.263086709088529</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>-5.46211498923229</v>
       </c>
       <c r="E40">
-        <v>-22.04857143232961</v>
+        <v>-20.60069602327918</v>
       </c>
       <c r="F40">
-        <v>1.930353947858124</v>
+        <v>2.429450948579289</v>
       </c>
       <c r="G40">
-        <v>-5.839214204836717</v>
+        <v>-3.262368320706508</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>-5.638983066037071</v>
       </c>
       <c r="E41">
-        <v>-21.65732939196292</v>
+        <v>-21.11374495750419</v>
       </c>
       <c r="F41">
-        <v>2.169374763145822</v>
+        <v>2.1785016603365</v>
       </c>
       <c r="G41">
-        <v>-5.634533105780198</v>
+        <v>-3.665821195031948</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>-5.866670789331477</v>
       </c>
       <c r="E42">
-        <v>-21.67427947017363</v>
+        <v>-19.6268612733517</v>
       </c>
       <c r="F42">
-        <v>2.1565198222302</v>
+        <v>1.931978830127365</v>
       </c>
       <c r="G42">
-        <v>-5.911317886682044</v>
+        <v>-3.36369749857252</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>-6.137300285807838</v>
       </c>
       <c r="E43">
-        <v>-20.61473429270296</v>
+        <v>-19.26593283799236</v>
       </c>
       <c r="F43">
-        <v>2.130689578749383</v>
+        <v>2.391744494438591</v>
       </c>
       <c r="G43">
-        <v>-5.589324295895911</v>
+        <v>-2.933631148656878</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>-6.443589451163028</v>
       </c>
       <c r="E44">
-        <v>-19.04564974836324</v>
+        <v>-18.38030370478627</v>
       </c>
       <c r="F44">
-        <v>2.177711391084696</v>
+        <v>2.124422854441989</v>
       </c>
       <c r="G44">
-        <v>-5.305511226814192</v>
+        <v>-3.122461355671368</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>-6.768304770845623</v>
       </c>
       <c r="E45">
-        <v>-20.20549609662979</v>
+        <v>-18.07781975496992</v>
       </c>
       <c r="F45">
-        <v>2.248878383806798</v>
+        <v>2.32579264529603</v>
       </c>
       <c r="G45">
-        <v>-5.530922962037628</v>
+        <v>-2.785192907767037</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>-7.096165518787448</v>
       </c>
       <c r="E46">
-        <v>-19.24756987589125</v>
+        <v>-16.941372031901</v>
       </c>
       <c r="F46">
-        <v>2.473158064433586</v>
+        <v>2.303456057064672</v>
       </c>
       <c r="G46">
-        <v>-5.437267628731646</v>
+        <v>-2.89746674918588</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>-7.407874768672365</v>
       </c>
       <c r="E47">
-        <v>-18.09719256677474</v>
+        <v>-17.5492336264246</v>
       </c>
       <c r="F47">
-        <v>2.143443162486417</v>
+        <v>1.910375497734855</v>
       </c>
       <c r="G47">
-        <v>-6.169835077298192</v>
+        <v>-3.873594343622146</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>-7.689541303865489</v>
       </c>
       <c r="E48">
-        <v>-17.99742122743774</v>
+        <v>-16.18823246273733</v>
       </c>
       <c r="F48">
-        <v>1.932021590187081</v>
+        <v>2.183713636504211</v>
       </c>
       <c r="G48">
-        <v>-5.345515859110745</v>
+        <v>-3.822837059414041</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>-7.926879999641082</v>
       </c>
       <c r="E49">
-        <v>-17.46653463409652</v>
+        <v>-15.18296104624859</v>
       </c>
       <c r="F49">
-        <v>1.785310241592602</v>
+        <v>1.774938551552389</v>
       </c>
       <c r="G49">
-        <v>-5.039227496362914</v>
+        <v>-3.999024293014053</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>-8.112282920562643</v>
       </c>
       <c r="E50">
-        <v>-16.17803433927205</v>
+        <v>-15.49897154792585</v>
       </c>
       <c r="F50">
-        <v>2.091473852871272</v>
+        <v>2.366416285732968</v>
       </c>
       <c r="G50">
-        <v>-5.700293782372281</v>
+        <v>-4.030971057468021</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>-8.240863548393298</v>
       </c>
       <c r="E51">
-        <v>-16.69851902781765</v>
+        <v>-14.87252962454878</v>
       </c>
       <c r="F51">
-        <v>1.834509649561644</v>
+        <v>1.548824939475522</v>
       </c>
       <c r="G51">
-        <v>-5.595607711329447</v>
+        <v>-3.701042089024254</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>-8.314466267992346</v>
       </c>
       <c r="E52">
-        <v>-16.85622766360878</v>
+        <v>-15.60220264140471</v>
       </c>
       <c r="F52">
-        <v>1.491974648228992</v>
+        <v>1.637284417088308</v>
       </c>
       <c r="G52">
-        <v>-5.876590263975089</v>
+        <v>-4.102286829475</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-8.339003991501002</v>
       </c>
       <c r="E53">
-        <v>-16.53005526625831</v>
+        <v>-15.12730157222032</v>
       </c>
       <c r="F53">
-        <v>1.868133309852339</v>
+        <v>1.617698726032068</v>
       </c>
       <c r="G53">
-        <v>-5.179912439599782</v>
+        <v>-3.303875940677889</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>-8.324649051820996</v>
       </c>
       <c r="E54">
-        <v>-15.07918653588882</v>
+        <v>-14.38457749327429</v>
       </c>
       <c r="F54">
-        <v>1.620307089674797</v>
+        <v>1.781110253504857</v>
       </c>
       <c r="G54">
-        <v>-6.008978980090544</v>
+        <v>-3.439005788499861</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-8.283483912970883</v>
       </c>
       <c r="E55">
-        <v>-15.49612766624904</v>
+        <v>-13.20178083873686</v>
       </c>
       <c r="F55">
-        <v>1.533694213159414</v>
+        <v>1.533657787923358</v>
       </c>
       <c r="G55">
-        <v>-5.40422507370418</v>
+        <v>-2.939590130627566</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-8.226637778026159</v>
       </c>
       <c r="E56">
-        <v>-15.17276292278332</v>
+        <v>-13.00423521710025</v>
       </c>
       <c r="F56">
-        <v>1.71841450372444</v>
+        <v>1.371301008590253</v>
       </c>
       <c r="G56">
-        <v>-5.991830354197119</v>
+        <v>-3.887306623245808</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-8.164836023532439</v>
       </c>
       <c r="E57">
-        <v>-14.90266661906983</v>
+        <v>-12.34987525146589</v>
       </c>
       <c r="F57">
-        <v>1.613802809480087</v>
+        <v>2.02047314927029</v>
       </c>
       <c r="G57">
-        <v>-6.298770894416187</v>
+        <v>-3.706176745155664</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-8.104026048266489</v>
       </c>
       <c r="E58">
-        <v>-14.53402166400141</v>
+        <v>-12.64394982505</v>
       </c>
       <c r="F58">
-        <v>1.530621823683461</v>
+        <v>1.925338351223927</v>
       </c>
       <c r="G58">
-        <v>-6.204632221461472</v>
+        <v>-4.174711634237636</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-8.049891897769259</v>
       </c>
       <c r="E59">
-        <v>-14.62105893442884</v>
+        <v>-11.54968936583653</v>
       </c>
       <c r="F59">
-        <v>1.488507915980095</v>
+        <v>1.640977619283112</v>
       </c>
       <c r="G59">
-        <v>-5.749614289816343</v>
+        <v>-3.464612858246123</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-8.002555634303052</v>
       </c>
       <c r="E60">
-        <v>-15.34628046133522</v>
+        <v>-10.77672866594129</v>
       </c>
       <c r="F60">
-        <v>1.252640259170037</v>
+        <v>1.475171528466179</v>
       </c>
       <c r="G60">
-        <v>-6.405128790956352</v>
+        <v>-4.216192769844704</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-7.963958615478764</v>
       </c>
       <c r="E61">
-        <v>-14.09826019566532</v>
+        <v>-11.20365508148842</v>
       </c>
       <c r="F61">
-        <v>1.163480783542626</v>
+        <v>1.416696354950409</v>
       </c>
       <c r="G61">
-        <v>-6.166590742669706</v>
+        <v>-5.335028050842333</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-7.929582353921427</v>
       </c>
       <c r="E62">
-        <v>-13.44995027130521</v>
+        <v>-11.62869765184836</v>
       </c>
       <c r="F62">
-        <v>1.20066778214306</v>
+        <v>1.059043296948972</v>
       </c>
       <c r="G62">
-        <v>-6.335918525912349</v>
+        <v>-4.925510257088948</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-7.898446006371755</v>
       </c>
       <c r="E63">
-        <v>-13.4737383452675</v>
+        <v>-11.29455514024439</v>
       </c>
       <c r="F63">
-        <v>0.9975274080755576</v>
+        <v>1.142922697054307</v>
       </c>
       <c r="G63">
-        <v>-5.828034492550599</v>
+        <v>-5.36298229737594</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-7.862679251552208</v>
       </c>
       <c r="E64">
-        <v>-13.12580210183616</v>
+        <v>-10.02909119269694</v>
       </c>
       <c r="F64">
-        <v>1.027190219871738</v>
+        <v>1.047989029659205</v>
       </c>
       <c r="G64">
-        <v>-6.185106623870849</v>
+        <v>-3.391532565466712</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-7.819224865120471</v>
       </c>
       <c r="E65">
-        <v>-12.31877822045522</v>
+        <v>-10.2997037424473</v>
       </c>
       <c r="F65">
-        <v>1.167345025976299</v>
+        <v>1.05022363870589</v>
       </c>
       <c r="G65">
-        <v>-5.857455310758102</v>
+        <v>-4.113850565043674</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-7.757698413163163</v>
       </c>
       <c r="E66">
-        <v>-13.10824067963442</v>
+        <v>-11.15393696535821</v>
       </c>
       <c r="F66">
-        <v>1.021938651056141</v>
+        <v>0.8422893868323521</v>
       </c>
       <c r="G66">
-        <v>-5.453860082974473</v>
+        <v>-4.801742201557756</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-7.674129045462896</v>
       </c>
       <c r="E67">
-        <v>-13.23287334127352</v>
+        <v>-10.64744978997031</v>
       </c>
       <c r="F67">
-        <v>1.128571154048595</v>
+        <v>1.120864841064066</v>
       </c>
       <c r="G67">
-        <v>-6.7702091319361</v>
+        <v>-3.942493417385458</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-7.557745250211448</v>
       </c>
       <c r="E68">
-        <v>-12.34219495954889</v>
+        <v>-9.089396608313274</v>
       </c>
       <c r="F68">
-        <v>0.7947306981917055</v>
+        <v>0.4354646357153937</v>
       </c>
       <c r="G68">
-        <v>-5.712009803035762</v>
+        <v>-4.331138221513739</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-7.406025215541912</v>
       </c>
       <c r="E69">
-        <v>-13.12367824752657</v>
+        <v>-10.11860100993255</v>
       </c>
       <c r="F69">
-        <v>0.7637249037792321</v>
+        <v>0.9779908119026967</v>
       </c>
       <c r="G69">
-        <v>-5.80949543753068</v>
+        <v>-4.040776893355342</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-7.210867644319807</v>
       </c>
       <c r="E70">
-        <v>-12.27636000442537</v>
+        <v>-11.16147687458098</v>
       </c>
       <c r="F70">
-        <v>0.5602218610570939</v>
+        <v>0.1984202854101635</v>
       </c>
       <c r="G70">
-        <v>-5.977912820750023</v>
+        <v>-3.99063537061754</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-6.973805363968012</v>
       </c>
       <c r="E71">
-        <v>-11.95712522925465</v>
+        <v>-9.777670315791077</v>
       </c>
       <c r="F71">
-        <v>0.7212879200691166</v>
+        <v>0.5918706400712358</v>
       </c>
       <c r="G71">
-        <v>-5.640621199026918</v>
+        <v>-4.234665613953837</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-6.690746879654638</v>
       </c>
       <c r="E72">
-        <v>-12.42031566465521</v>
+        <v>-11.04457431807297</v>
       </c>
       <c r="F72">
-        <v>0.4801061380598008</v>
+        <v>0.5025488345874933</v>
       </c>
       <c r="G72">
-        <v>-5.875050860299329</v>
+        <v>-3.954239232958793</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-6.367885596162025</v>
       </c>
       <c r="E73">
-        <v>-13.06228119693057</v>
+        <v>-10.52177105083544</v>
       </c>
       <c r="F73">
-        <v>0.3696545282522652</v>
+        <v>0.5904880648070572</v>
       </c>
       <c r="G73">
-        <v>-5.312632210269164</v>
+        <v>-3.384080527457813</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-6.005616456132056</v>
       </c>
       <c r="E74">
-        <v>-12.41808765544343</v>
+        <v>-10.61193296832816</v>
       </c>
       <c r="F74">
-        <v>0.3450801635623913</v>
+        <v>0.184990459247237</v>
       </c>
       <c r="G74">
-        <v>-5.352557389472775</v>
+        <v>-3.475934923990431</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-5.613867511458437</v>
       </c>
       <c r="E75">
-        <v>-13.278615457225</v>
+        <v>-10.07573447497594</v>
       </c>
       <c r="F75">
-        <v>0.1548137348814961</v>
+        <v>0.6186780301018794</v>
       </c>
       <c r="G75">
-        <v>-5.400537125973432</v>
+        <v>-3.409449237925247</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-5.195592626812678</v>
       </c>
       <c r="E76">
-        <v>-13.79736121175165</v>
+        <v>-10.81229077232352</v>
       </c>
       <c r="F76">
-        <v>0.1057869508572371</v>
+        <v>0.01732430583262046</v>
       </c>
       <c r="G76">
-        <v>-4.846947700896504</v>
+        <v>-3.468602065620945</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-4.762427756408818</v>
       </c>
       <c r="E77">
-        <v>-14.21357778627064</v>
+        <v>-12.14278813509513</v>
       </c>
       <c r="F77">
-        <v>-0.02185578666239375</v>
+        <v>0.3173977760134675</v>
       </c>
       <c r="G77">
-        <v>-5.011604304383235</v>
+        <v>-3.134064817786513</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-4.318147839943343</v>
       </c>
       <c r="E78">
-        <v>-14.64668104036424</v>
+        <v>-12.88654923458892</v>
       </c>
       <c r="F78">
-        <v>-0.09491609980640406</v>
+        <v>0.007722296867311094</v>
       </c>
       <c r="G78">
-        <v>-4.02220804342557</v>
+        <v>-2.682609033141641</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>-3.874467860120512</v>
       </c>
       <c r="E79">
-        <v>-15.57111919581606</v>
+        <v>-12.88798928932336</v>
       </c>
       <c r="F79">
-        <v>0.03548466156496461</v>
+        <v>-0.03293222583497724</v>
       </c>
       <c r="G79">
-        <v>-4.269843470854132</v>
+        <v>-2.740811734267568</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>-3.434739940335312</v>
       </c>
       <c r="E80">
-        <v>-14.77038536483177</v>
+        <v>-13.16397260924682</v>
       </c>
       <c r="F80">
-        <v>-0.2015406842692803</v>
+        <v>0.1017999712151183</v>
       </c>
       <c r="G80">
-        <v>-4.162412957559243</v>
+        <v>-2.491984510444866</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>-3.010949621843849</v>
       </c>
       <c r="E81">
-        <v>-16.18028046237986</v>
+        <v>-13.66334102349465</v>
       </c>
       <c r="F81">
-        <v>0.06777167406302863</v>
+        <v>-0.2660782840293532</v>
       </c>
       <c r="G81">
-        <v>-3.776846960782485</v>
+        <v>-1.848881244531585</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>-2.606306724434576</v>
       </c>
       <c r="E82">
-        <v>-17.55748903454058</v>
+        <v>-14.24073504489464</v>
       </c>
       <c r="F82">
-        <v>-0.2615560117878158</v>
+        <v>0.08269651861012997</v>
       </c>
       <c r="G82">
-        <v>-3.684002711133625</v>
+        <v>-1.358615934529836</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>-2.232569531960542</v>
       </c>
       <c r="E83">
-        <v>-18.50299817955009</v>
+        <v>-16.33750455145217</v>
       </c>
       <c r="F83">
-        <v>-0.1608695326548799</v>
+        <v>-0.2595312437749265</v>
       </c>
       <c r="G83">
-        <v>-2.857005261604908</v>
+        <v>-1.655777123225897</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>-1.892901399232581</v>
       </c>
       <c r="E84">
-        <v>-19.44373884142952</v>
+        <v>-17.38054344116487</v>
       </c>
       <c r="F84">
-        <v>-0.2723370898071699</v>
+        <v>-0.1888623265632298</v>
       </c>
       <c r="G84">
-        <v>-2.398716510966979</v>
+        <v>-2.265841144657252</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>-1.599334971230028</v>
       </c>
       <c r="E85">
-        <v>-19.16011145738111</v>
+        <v>-17.35444131698466</v>
       </c>
       <c r="F85">
-        <v>-0.312147497256529</v>
+        <v>0.3377951163513698</v>
       </c>
       <c r="G85">
-        <v>-2.40516545367748</v>
+        <v>-1.711414151558888</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>-1.35449646385594</v>
       </c>
       <c r="E86">
-        <v>-21.19839119365556</v>
+        <v>-19.46384073754957</v>
       </c>
       <c r="F86">
-        <v>-0.3937384423140539</v>
+        <v>-0.4792949869838392</v>
       </c>
       <c r="G86">
-        <v>-2.733680819175977</v>
+        <v>-1.237062633964416</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>-1.169904411358272</v>
       </c>
       <c r="E87">
-        <v>-24.25558211012985</v>
+        <v>-21.33151474405905</v>
       </c>
       <c r="F87">
-        <v>-0.7384977586049404</v>
+        <v>-0.2311892427122222</v>
       </c>
       <c r="G87">
-        <v>-2.170103478207068</v>
+        <v>-0.571782023483557</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>-1.046303676627591</v>
       </c>
       <c r="E88">
-        <v>-24.41963060953172</v>
+        <v>-21.77505613074032</v>
       </c>
       <c r="F88">
-        <v>-0.6309324528282931</v>
+        <v>-0.5961043841889065</v>
       </c>
       <c r="G88">
-        <v>-2.808545496001056</v>
+        <v>-0.4630339130640377</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>-0.9932559997036786</v>
       </c>
       <c r="E89">
-        <v>-25.30399177001566</v>
+        <v>-23.4914111782835</v>
       </c>
       <c r="F89">
-        <v>-0.6427358130160633</v>
+        <v>-0.8164184652034343</v>
       </c>
       <c r="G89">
-        <v>-1.849480453274193</v>
+        <v>-1.211366179488593</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>-1.008027549265109</v>
       </c>
       <c r="E90">
-        <v>-26.63900402137291</v>
+        <v>-24.70715248122673</v>
       </c>
       <c r="F90">
-        <v>-0.4950496934306308</v>
+        <v>-0.5347927933785838</v>
       </c>
       <c r="G90">
-        <v>-2.028974921867937</v>
+        <v>-1.059819336337376</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>-1.096402065547005</v>
       </c>
       <c r="E91">
-        <v>-29.13691028400388</v>
+        <v>-26.56096935727273</v>
       </c>
       <c r="F91">
-        <v>-0.6714753242635429</v>
+        <v>-0.5957868511528609</v>
       </c>
       <c r="G91">
-        <v>-2.0977349527186</v>
+        <v>-0.05170525090067131</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>-1.250921199331754</v>
       </c>
       <c r="E92">
-        <v>-30.62923040120258</v>
+        <v>-30.40066020413943</v>
       </c>
       <c r="F92">
-        <v>-1.110656770938845</v>
+        <v>-0.7763958411614064</v>
       </c>
       <c r="G92">
-        <v>-2.526086440044899</v>
+        <v>-1.269744339528101</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>-1.473887235210652</v>
       </c>
       <c r="E93">
-        <v>-32.25948783667492</v>
+        <v>-29.88795996241301</v>
       </c>
       <c r="F93">
-        <v>-1.042659565606494</v>
+        <v>-0.8722330127812667</v>
       </c>
       <c r="G93">
-        <v>-2.30091637464583</v>
+        <v>-0.6990294623765236</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>-1.754385817450724</v>
       </c>
       <c r="E94">
-        <v>-34.3705197721196</v>
+        <v>-33.71453408431648</v>
       </c>
       <c r="F94">
-        <v>-1.002590222239961</v>
+        <v>-1.080350974540995</v>
       </c>
       <c r="G94">
-        <v>-2.231706109601827</v>
+        <v>0.1822907289060947</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>-2.090137016563818</v>
       </c>
       <c r="E95">
-        <v>-37.07192886394427</v>
+        <v>-35.0586168691111</v>
       </c>
       <c r="F95">
-        <v>-1.022326365358167</v>
+        <v>-1.011827186991761</v>
       </c>
       <c r="G95">
-        <v>-3.103121148630946</v>
+        <v>-0.7492669909349639</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>-2.470704909343138</v>
       </c>
       <c r="E96">
-        <v>-38.71048019956165</v>
+        <v>-38.10087061407109</v>
       </c>
       <c r="F96">
-        <v>-0.8765897877546407</v>
+        <v>-0.7546024640590441</v>
       </c>
       <c r="G96">
-        <v>-3.135551252733646</v>
+        <v>-0.6567471747489519</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>-2.885774339524976</v>
       </c>
       <c r="E97">
-        <v>-41.55993642788208</v>
+        <v>-40.34383737549224</v>
       </c>
       <c r="F97">
-        <v>-1.298236442534197</v>
+        <v>-0.6814273322361645</v>
       </c>
       <c r="G97">
-        <v>-3.69838041041068</v>
+        <v>-1.727718588339799</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>-3.328316945076707</v>
       </c>
       <c r="E98">
-        <v>-43.87734903775232</v>
+        <v>-41.67306223706769</v>
       </c>
       <c r="F98">
-        <v>-1.250374474210744</v>
+        <v>-0.6262027151118332</v>
       </c>
       <c r="G98">
-        <v>-3.245471296274067</v>
+        <v>-1.769156686854856</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>-3.774164592979098</v>
       </c>
       <c r="E99">
-        <v>-45.3427337915534</v>
+        <v>-45.23393720351913</v>
       </c>
       <c r="F99">
-        <v>-1.05534663369508</v>
+        <v>-0.8851956456991387</v>
       </c>
       <c r="G99">
-        <v>-4.239796959539707</v>
+        <v>-2.035927067500407</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>-4.227460355630225</v>
       </c>
       <c r="E100">
-        <v>-48.21057562434497</v>
+        <v>-46.81068845435384</v>
       </c>
       <c r="F100">
-        <v>-1.463363915366364</v>
+        <v>-1.154452574324407</v>
       </c>
       <c r="G100">
-        <v>-4.118170826972423</v>
+        <v>-2.907520875988647</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-4.638712216464555</v>
       </c>
       <c r="E101">
-        <v>-50.3734121703189</v>
+        <v>-49.16266350996912</v>
       </c>
       <c r="F101">
-        <v>-1.460259851772103</v>
+        <v>-1.000276427897504</v>
       </c>
       <c r="G101">
-        <v>-4.947654496201134</v>
+        <v>-2.045368743378408</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-5.05197128002231</v>
       </c>
       <c r="E102">
-        <v>-51.84312614527131</v>
+        <v>-50.64208313683847</v>
       </c>
       <c r="F102">
-        <v>-1.531371414787165</v>
+        <v>-1.387835396553141</v>
       </c>
       <c r="G102">
-        <v>-4.971361312807854</v>
+        <v>-1.654241030095675</v>
       </c>
     </row>
   </sheetData>
